--- a/exports/SUPREMEIND_full_report.xlsx
+++ b/exports/SUPREMEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.65</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2238</v>
+        <v>2120</v>
       </c>
       <c r="I2" t="n">
         <v>2183.231550755993</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>-3.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.41</v>
+        <v>4.57</v>
       </c>
       <c r="M2" t="n">
         <v>0.16</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>4.83</v>
       </c>
       <c r="O2" t="n">
         <v>0.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44614.55208333334</v>
+        <v>44615.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2045.75</v>
+        <v>2056.45</v>
       </c>
       <c r="I3" t="n">
         <v>2047.43196530477</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.09</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2044.45</v>
+        <v>1994</v>
       </c>
       <c r="I4" t="n">
         <v>2025.467090863761</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.58</v>
+        <v>-3.04</v>
       </c>
       <c r="L4" t="n">
         <v>5.9</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1831.6</v>
+        <v>1835.5</v>
       </c>
       <c r="I5" t="n">
         <v>1835.340628414848</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="L5" t="n">
         <v>2.54</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1805.9</v>
+        <v>1770</v>
       </c>
       <c r="I6" t="n">
         <v>1770.144981075078</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.61</v>
+        <v>-3.57</v>
       </c>
       <c r="L6" t="n">
-        <v>1.93</v>
+        <v>4.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="N6" t="n">
         <v>2.79</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.18</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1777</v>
+        <v>1840</v>
       </c>
       <c r="I7" t="n">
         <v>1798.572394926622</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4</v>
+        <v>-3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>4.63</v>
       </c>
       <c r="M7" t="n">
         <v>0.77</v>
       </c>
       <c r="N7" t="n">
-        <v>3.49</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
         <v>-1.45</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.56</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1814</v>
+        <v>1787.55</v>
       </c>
       <c r="I8" t="n">
         <v>1804.44319968052</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.41</v>
+        <v>-2.85</v>
       </c>
       <c r="L8" t="n">
         <v>3.46</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1900</v>
+        <v>1966</v>
       </c>
       <c r="I9" t="n">
         <v>1909.609861363198</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.29</v>
+        <v>-9.98</v>
       </c>
       <c r="L9" t="n">
-        <v>8.08</v>
+        <v>10.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.51</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>-1.75</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.56</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1911</v>
+        <v>1856</v>
       </c>
       <c r="I10" t="n">
         <v>1876.783616639343</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.8</v>
+        <v>-5.6</v>
       </c>
       <c r="L10" t="n">
-        <v>3.26</v>
+        <v>5.83</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0.58</v>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>3.72</v>
       </c>
       <c r="O10" t="n">
         <v>3.95</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1946.95</v>
+        <v>1967.95</v>
       </c>
       <c r="I11" t="n">
         <v>1951.414831228053</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.9</v>
+        <v>-6.03</v>
       </c>
       <c r="L11" t="n">
-        <v>6.03</v>
+        <v>6.41</v>
       </c>
       <c r="M11" t="n">
         <v>0.93</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2038.35</v>
+        <v>2003.35</v>
       </c>
       <c r="I12" t="n">
         <v>2009.246084700436</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>3.58</v>
+        <v>1.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.42</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44854.38541666666</v>
+        <v>44854.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2055.3</v>
+        <v>2060</v>
       </c>
       <c r="I13" t="n">
         <v>2058.185876884512</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.59</v>
+        <v>-2.83</v>
       </c>
       <c r="L13" t="n">
         <v>6.82</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.22</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44882.38541666666</v>
+        <v>44882.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2306.1</v>
+        <v>2279</v>
       </c>
       <c r="I14" t="n">
         <v>2281.025814881779</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K14" t="n">
-        <v>11.95</v>
+        <v>10.63</v>
       </c>
       <c r="L14" t="n">
         <v>5.23</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2350.05</v>
+        <v>2440.95</v>
       </c>
       <c r="I15" t="n">
         <v>2424.238974789416</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.12</v>
+        <v>-7.11</v>
       </c>
       <c r="L15" t="n">
-        <v>5.97</v>
+        <v>7.59</v>
       </c>
       <c r="M15" t="n">
         <v>0.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.24</v>
+        <v>4.04</v>
       </c>
       <c r="O15" t="n">
         <v>-3.64</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2427.95</v>
+        <v>2350</v>
       </c>
       <c r="I16" t="n">
         <v>2415.293120620798</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.53</v>
+        <v>-3.73</v>
       </c>
       <c r="L16" t="n">
-        <v>3.74</v>
+        <v>4.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.29</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2410</v>
+        <v>2508.95</v>
       </c>
       <c r="I17" t="n">
         <v>2487.805728378055</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.55</v>
+        <v>-6.76</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.85</v>
       </c>
       <c r="M17" t="n">
         <v>2.96</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>5.31</v>
       </c>
       <c r="O17" t="n">
         <v>-2.5</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2669.95</v>
+        <v>2580.8</v>
       </c>
       <c r="I18" t="n">
         <v>2603.813937587845</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>6.42</v>
+        <v>2.86</v>
       </c>
       <c r="L18" t="n">
         <v>3.7</v>
@@ -1467,7 +1682,7 @@
         <v>2.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.88</v>
+        <v>5.35</v>
       </c>
       <c r="O18" t="n">
         <v>5.31</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45005.38541666666</v>
+        <v>45005.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2563.75</v>
+        <v>2671</v>
       </c>
       <c r="I19" t="n">
         <v>2670.126985991642</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.66</v>
+        <v>-3.5</v>
       </c>
       <c r="L19" t="n">
         <v>4.04</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45135.38541666666</v>
+        <v>45135.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>3482.95</v>
+        <v>3386</v>
       </c>
       <c r="I20" t="n">
         <v>3477.789318711132</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>129.8333333333333</v>
+        <v>130</v>
       </c>
       <c r="K20" t="n">
-        <v>30.4</v>
+        <v>26.77</v>
       </c>
       <c r="L20" t="n">
         <v>8.98</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.27</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3580</v>
+        <v>3715.6</v>
       </c>
       <c r="I21" t="n">
         <v>3699.773836659585</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.73</v>
+        <v>-9.73</v>
       </c>
       <c r="L21" t="n">
-        <v>7.21</v>
+        <v>10.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.24</v>
       </c>
       <c r="N21" t="n">
-        <v>4.67</v>
+        <v>4.89</v>
       </c>
       <c r="O21" t="n">
         <v>-7.17</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.84</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45183.55208333334</v>
+        <v>45184.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4280</v>
+        <v>4177.3</v>
       </c>
       <c r="I22" t="n">
         <v>4252.501411791953</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>15.19</v>
+        <v>12.43</v>
       </c>
       <c r="L22" t="n">
         <v>3.67</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.53</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45210.38541666666</v>
+        <v>45210.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>4098.3</v>
+        <v>4130</v>
       </c>
       <c r="I23" t="n">
         <v>4108.952609236813</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.89</v>
+        <v>1.13</v>
       </c>
       <c r="L23" t="n">
         <v>3.36</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.71</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>4500.5</v>
+        <v>4240</v>
       </c>
       <c r="I24" t="n">
         <v>4335.921578735013</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>8.970000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="L24" t="n">
         <v>0.9399999999999999</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.12</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45260.38541666666</v>
+        <v>45260.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>4257.75</v>
+        <v>4450</v>
       </c>
       <c r="I25" t="n">
         <v>4340.921666588913</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.42</v>
+        <v>-4.95</v>
       </c>
       <c r="L25" t="n">
         <v>9.43</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.85</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45300.38541666666</v>
+        <v>45300.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>4305.15</v>
+        <v>4290</v>
       </c>
       <c r="I26" t="n">
         <v>4298.788508165767</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.26</v>
+        <v>-3.6</v>
       </c>
       <c r="L26" t="n">
         <v>4.61</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3960</v>
+        <v>4071.15</v>
       </c>
       <c r="I27" t="n">
         <v>4032.367297200319</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>7.69</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.73</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3910.9</v>
+        <v>3712.85</v>
       </c>
       <c r="I28" t="n">
         <v>3842.880769272626</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.94</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L28" t="n">
         <v>10.86</v>
@@ -2037,7 +2372,7 @@
         <v>2.22</v>
       </c>
       <c r="N28" t="n">
-        <v>2.52</v>
+        <v>4.14</v>
       </c>
       <c r="O28" t="n">
         <v>2.07</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.14</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45365.38541666666</v>
+        <v>45365.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>3870.1</v>
+        <v>4025</v>
       </c>
       <c r="I29" t="n">
         <v>4021.969471463134</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.24</v>
+        <v>-8.41</v>
       </c>
       <c r="L29" t="n">
-        <v>5.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>5782.5</v>
+        <v>5726.1</v>
       </c>
       <c r="I30" t="n">
         <v>5729.749774343418</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>124</v>
+        <v>125.8333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>43.66</v>
+        <v>42.26</v>
       </c>
       <c r="L30" t="n">
         <v>7.28</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45524.38541666666</v>
+        <v>45524.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>5332.9</v>
+        <v>5495</v>
       </c>
       <c r="I31" t="n">
         <v>5350.812517249441</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>6.87</v>
+        <v>4.04</v>
       </c>
       <c r="L31" t="n">
         <v>2.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>5260</v>
+        <v>5237.6</v>
       </c>
       <c r="I32" t="n">
         <v>5242.006207348049</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.28</v>
+        <v>-4.68</v>
       </c>
       <c r="L32" t="n">
         <v>4.91</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.71</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>5405.05</v>
+        <v>5550.1</v>
       </c>
       <c r="I33" t="n">
         <v>5520.529591719141</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.2</v>
+        <v>-5.97</v>
       </c>
       <c r="L33" t="n">
-        <v>4.84</v>
+        <v>7.21</v>
       </c>
       <c r="M33" t="n">
         <v>1.17</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.8</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45583.38541666666</v>
+        <v>45583.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>5195.9</v>
+        <v>5079.9</v>
       </c>
       <c r="I34" t="n">
         <v>5117.1228430739</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.38</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>7.72</v>
+        <v>11.08</v>
       </c>
       <c r="M34" t="n">
         <v>0.78</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4380</v>
+        <v>4661</v>
       </c>
       <c r="I35" t="n">
         <v>4578.79954582407</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>13.78</v>
+        <v>8.25</v>
       </c>
       <c r="L35" t="n">
         <v>2.77</v>
@@ -2436,7 +2855,7 @@
         <v>3.16</v>
       </c>
       <c r="N35" t="n">
-        <v>4.09</v>
+        <v>7.31</v>
       </c>
       <c r="O35" t="n">
         <v>-3.22</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.93</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45646.55208333334</v>
+        <v>45649.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4850</v>
+        <v>4759.45</v>
       </c>
       <c r="I36" t="n">
         <v>4803.273259067605</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
-        <v>4.05</v>
+        <v>2.11</v>
       </c>
       <c r="L36" t="n">
         <v>5.39</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.83</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3812</v>
+        <v>3932.95</v>
       </c>
       <c r="I37" t="n">
         <v>3904.521925095789</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K37" t="n">
-        <v>19.91</v>
+        <v>17.37</v>
       </c>
       <c r="L37" t="n">
         <v>2.14</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>10.68</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45702.55208333334</v>
+        <v>45705.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3759.2</v>
+        <v>3542.05</v>
       </c>
       <c r="I38" t="n">
         <v>3669.045467410632</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.42</v>
+        <v>-9.94</v>
       </c>
       <c r="L38" t="n">
-        <v>8.77</v>
+        <v>10.28</v>
       </c>
       <c r="M38" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="N38" t="n">
         <v>5.53</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>12.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3436.4</v>
+        <v>3569.1</v>
       </c>
       <c r="I39" t="n">
         <v>3561.965028217817</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>2.98</v>
+        <v>-0.76</v>
       </c>
       <c r="L39" t="n">
         <v>8.02</v>
       </c>
       <c r="M39" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="N39" t="n">
         <v>5.49</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>8.01</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3423</v>
+        <v>3279</v>
       </c>
       <c r="I40" t="n">
         <v>3298.862506530309</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.09</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>6.94</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0.97</v>
       </c>
       <c r="N40" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="O40" t="n">
         <v>1.85</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3330.6</v>
+        <v>3385.1</v>
       </c>
       <c r="I41" t="n">
         <v>3374.994385019905</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.57</v>
+        <v>-3.24</v>
       </c>
       <c r="L41" t="n">
         <v>4.66</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45835.38541666666</v>
+        <v>45835.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>4366.4</v>
+        <v>4321.5</v>
       </c>
       <c r="I42" t="n">
         <v>4351.707846041925</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>72.83333333333333</v>
+        <v>73</v>
       </c>
       <c r="K42" t="n">
-        <v>28.99</v>
+        <v>27.66</v>
       </c>
       <c r="L42" t="n">
         <v>3.61</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>4216</v>
+        <v>4336.1</v>
       </c>
       <c r="I43" t="n">
         <v>4279.792511715766</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>2.44</v>
+        <v>-0.34</v>
       </c>
       <c r="L43" t="n">
         <v>2.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>4202</v>
+        <v>4072.3</v>
       </c>
       <c r="I44" t="n">
         <v>4096.367994489781</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.09</v>
+        <v>-6.08</v>
       </c>
       <c r="L44" t="n">
-        <v>3.78</v>
+        <v>6.25</v>
       </c>
       <c r="M44" t="n">
         <v>-0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.33</v>
+        <v>2.67</v>
       </c>
       <c r="O44" t="n">
         <v>-0.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4315</v>
+        <v>4334.2</v>
       </c>
       <c r="I45" t="n">
         <v>4327.02903201695</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.96</v>
+        <v>-6.43</v>
       </c>
       <c r="L45" t="n">
-        <v>6.63</v>
+        <v>7.11</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.18</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>4457.7</v>
+        <v>4410.7</v>
       </c>
       <c r="I46" t="n">
         <v>4422.757417936224</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>2.85</v>
+        <v>1.77</v>
       </c>
       <c r="L46" t="n">
         <v>5.32</v>
@@ -3063,7 +3614,7 @@
         <v>0.88</v>
       </c>
       <c r="N46" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="O46" t="n">
         <v>0.22</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.34</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45912.38541666666</v>
+        <v>45912.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>4485.3</v>
+        <v>4535</v>
       </c>
       <c r="I47" t="n">
         <v>4504.719136069404</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.69</v>
+        <v>-2.82</v>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>3.12</v>
       </c>
       <c r="M47" t="n">
         <v>0.17</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.85</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>4398.2</v>
+        <v>4366</v>
       </c>
       <c r="I48" t="n">
         <v>4368.581598104593</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.02</v>
+        <v>-3.73</v>
       </c>
       <c r="L48" t="n">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="M48" t="n">
         <v>0.32</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.15</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3284</v>
+        <v>3410.4</v>
       </c>
       <c r="I49" t="n">
         <v>3362.186031414944</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>24.78</v>
+        <v>21.89</v>
       </c>
       <c r="L49" t="n">
         <v>1.1</v>
@@ -3234,7 +3821,7 @@
         <v>5.48</v>
       </c>
       <c r="N49" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="O49" t="n">
         <v>-1.35</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3500.8</v>
+        <v>3472.1</v>
       </c>
       <c r="I50" t="n">
         <v>3486.08543401992</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>2.65</v>
+        <v>1.81</v>
       </c>
       <c r="L50" t="n">
         <v>4.51</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.31</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46055.38541666666</v>
+        <v>46055.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>3532.9</v>
+        <v>3608</v>
       </c>
       <c r="I51" t="n">
         <v>3534.207542387837</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.75</v>
+        <v>-3.91</v>
       </c>
       <c r="L51" t="n">
-        <v>3.65</v>
+        <v>3.97</v>
       </c>
       <c r="M51" t="n">
         <v>0.29</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.32</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3952</v>
+        <v>3788</v>
       </c>
       <c r="I52" t="n">
         <v>3873.227288661561</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>9.529999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="L52" t="n">
         <v>2.43</v>
@@ -3405,7 +4028,7 @@
         <v>2.52</v>
       </c>
       <c r="N52" t="n">
-        <v>2.13</v>
+        <v>3.19</v>
       </c>
       <c r="O52" t="n">
         <v>3.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>3592.1</v>
+        <v>3615</v>
       </c>
       <c r="I53" t="n">
         <v>3602.872776252532</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="L53" t="n">
         <v>7.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.51</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46184.38541666666</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>3457.9</v>
+        <v>3437.9</v>
       </c>
       <c r="I54" t="n">
         <v>3448.952787804635</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.35</v>
+        <v>-4.9</v>
       </c>
       <c r="L54" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="M54" t="n">
         <v>1.05</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.43</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3328</v>
+        <v>3405.5</v>
       </c>
       <c r="I55" t="n">
         <v>3348.276944339393</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>3.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L55" t="n">
         <v>6.05</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.06</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46230.38541666666</v>
+        <v>46230.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>3389.2</v>
+        <v>3330</v>
       </c>
       <c r="I56" t="n">
         <v>3351.485210565276</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.48</v>
+        <v>-2.22</v>
       </c>
       <c r="L56" t="n">
         <v>3.83</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46248.38541666666</v>
+        <v>46248.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>3501</v>
+        <v>3558.5</v>
       </c>
       <c r="I57" t="n">
         <v>3552.079346233035</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.14</v>
+        <v>-6.86</v>
       </c>
       <c r="L57" t="n">
-        <v>7.15</v>
+        <v>7.66</v>
       </c>
       <c r="M57" t="n">
         <v>0.89</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.27</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>3524.6</v>
+        <v>3481</v>
       </c>
       <c r="I58" t="n">
         <v>3511.739552140667</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.95</v>
+        <v>-2.18</v>
       </c>
       <c r="L58" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="M58" t="n">
         <v>2.72</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.22</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3470</v>
+        <v>3529.7</v>
       </c>
       <c r="I59" t="n">
         <v>3476.964896971275</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>0.32</v>
+        <v>-1.4</v>
       </c>
       <c r="L59" t="n">
         <v>3.51</v>
       </c>
       <c r="M59" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="N59" t="n">
         <v>4.36</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.65</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3475</v>
+        <v>3323.8</v>
       </c>
       <c r="I60" t="n">
         <v>3351.650683902591</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.55</v>
+        <v>-5.83</v>
       </c>
       <c r="L60" t="n">
-        <v>2.93</v>
+        <v>6.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="N60" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="O60" t="n">
         <v>1.16</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46301.55208333334</v>
+        <v>46302.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>3526</v>
+        <v>3581.5</v>
       </c>
       <c r="I61" t="n">
         <v>3556.24013976151</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.08</v>
+        <v>-7.75</v>
       </c>
       <c r="L61" t="n">
-        <v>6.22</v>
+        <v>9.27</v>
       </c>
       <c r="M61" t="n">
         <v>0.35</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>7.44</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>3530</v>
+        <v>3398.6</v>
       </c>
       <c r="I62" t="n">
         <v>3442.740853301374</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.44</v>
+        <v>-5.11</v>
       </c>
       <c r="L62" t="n">
-        <v>4.67</v>
+        <v>5.2</v>
       </c>
       <c r="M62" t="n">
-        <v>0.74</v>
+        <v>1.9</v>
       </c>
       <c r="N62" t="n">
-        <v>2.02</v>
+        <v>4.53</v>
       </c>
       <c r="O62" t="n">
         <v>0.58</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,12 @@
       <c r="Q63" t="n">
         <v>6</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6898,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6908,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6918,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129.8</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6928,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6938,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6948,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -6227,7 +6988,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.75</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +6998,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.93</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.52</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7018,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>43.66</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7028,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.3</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7038,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.76</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7048,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.61</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="21">
@@ -6297,7 +7058,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.86</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="22">
@@ -6307,7 +7068,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7078,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7088,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="25">
@@ -6347,7 +7108,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.74</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="27">
@@ -6367,7 +7128,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
